--- a/code/python/functions/bid_list/bid_lists/Bid List00002811.xlsx
+++ b/code/python/functions/bid_list/bid_lists/Bid List00002811.xlsx
@@ -693,9 +693,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
-    <numFmt numFmtId="1293" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="1294" formatCode="0.000"/>
-    <numFmt numFmtId="1295" formatCode="0.0000"/>
+    <numFmt numFmtId="5033" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="5034" formatCode="0.000"/>
+    <numFmt numFmtId="5035" formatCode="0.0000"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -842,14 +842,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="0"/>
+      <b/>
       <i val="0"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
+      <b val="0"/>
       <i val="0"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1144,6 +1144,7 @@
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyBorder="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyBorder="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyBorder="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
@@ -1180,7 +1181,6 @@
     <xf numFmtId="0" fontId="11" fillId="30" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyFill="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyBorder="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="7" applyFont="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
@@ -1189,85 +1189,85 @@
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="5033" fontId="18" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="5034" fontId="18" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="5035" fontId="18" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="5034" fontId="19" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="1293" fontId="19" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1294" fontId="19" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1295" fontId="19" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="5035" fontId="19" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="2" fontId="19" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1294" fontId="18" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1295" fontId="18" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="1293" fontId="18" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="5033" fontId="19" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="Normal" xfId="37"/>
-    <cellStyle name="20% - Accent 1" xfId="1" builtinId="30"/>
-    <cellStyle name="20% - Accent 2" xfId="2" builtinId="34"/>
-    <cellStyle name="20% - Accent 3" xfId="3" builtinId="38"/>
-    <cellStyle name="20% - Accent 4" xfId="4" builtinId="42"/>
-    <cellStyle name="20% - Accent 5" xfId="5" builtinId="46"/>
-    <cellStyle name="20% - Accent 6" xfId="6" builtinId="50"/>
-    <cellStyle name="40% - Accent 1" xfId="7" builtinId="31"/>
-    <cellStyle name="40% - Accent 2" xfId="8" builtinId="35"/>
-    <cellStyle name="40% - Accent 3" xfId="9" builtinId="39"/>
-    <cellStyle name="40% - Accent 4" xfId="10" builtinId="43"/>
-    <cellStyle name="40% - Accent 5" xfId="11" builtinId="47"/>
-    <cellStyle name="40% - Accent 6" xfId="12" builtinId="51"/>
-    <cellStyle name="60% - Accent 1" xfId="13" builtinId="32"/>
-    <cellStyle name="60% - Accent 2" xfId="14" builtinId="36"/>
-    <cellStyle name="60% - Accent 3" xfId="15" builtinId="40"/>
-    <cellStyle name="60% - Accent 4" xfId="16" builtinId="44"/>
-    <cellStyle name="60% - Accent 5" xfId="17" builtinId="48"/>
-    <cellStyle name="60% - Accent 6" xfId="18" builtinId="52"/>
-    <cellStyle name="Accent 1" xfId="19" builtinId="29"/>
-    <cellStyle name="Accent 2" xfId="20" builtinId="33"/>
-    <cellStyle name="Accent 3" xfId="21" builtinId="37"/>
-    <cellStyle name="Accent 4" xfId="22" builtinId="41"/>
-    <cellStyle name="Accent 5" xfId="23" builtinId="45"/>
-    <cellStyle name="Accent 6" xfId="24" builtinId="49"/>
-    <cellStyle name="Bad" xfId="25" builtinId="27"/>
-    <cellStyle name="Calculation" xfId="26" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="27" builtinId="23"/>
-    <cellStyle name="Explanatory Text" xfId="28" builtinId="53"/>
-    <cellStyle name="Good" xfId="29" builtinId="26"/>
-    <cellStyle name="Heading 1" xfId="30" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="31" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="32" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="33" builtinId="19"/>
-    <cellStyle name="Input" xfId="34" builtinId="20"/>
-    <cellStyle name="Linked Cell" xfId="35" builtinId="24"/>
-    <cellStyle name="Neutral" xfId="36" builtinId="28"/>
+    <cellStyle name="Normal" xfId="1"/>
+    <cellStyle name="20% - Accent 1" xfId="2" builtinId="30"/>
+    <cellStyle name="20% - Accent 2" xfId="3" builtinId="34"/>
+    <cellStyle name="20% - Accent 3" xfId="4" builtinId="38"/>
+    <cellStyle name="20% - Accent 4" xfId="5" builtinId="42"/>
+    <cellStyle name="20% - Accent 5" xfId="6" builtinId="46"/>
+    <cellStyle name="20% - Accent 6" xfId="7" builtinId="50"/>
+    <cellStyle name="40% - Accent 1" xfId="8" builtinId="31"/>
+    <cellStyle name="40% - Accent 2" xfId="9" builtinId="35"/>
+    <cellStyle name="40% - Accent 3" xfId="10" builtinId="39"/>
+    <cellStyle name="40% - Accent 4" xfId="11" builtinId="43"/>
+    <cellStyle name="40% - Accent 5" xfId="12" builtinId="47"/>
+    <cellStyle name="40% - Accent 6" xfId="13" builtinId="51"/>
+    <cellStyle name="60% - Accent 1" xfId="14" builtinId="32"/>
+    <cellStyle name="60% - Accent 2" xfId="15" builtinId="36"/>
+    <cellStyle name="60% - Accent 3" xfId="16" builtinId="40"/>
+    <cellStyle name="60% - Accent 4" xfId="17" builtinId="44"/>
+    <cellStyle name="60% - Accent 5" xfId="18" builtinId="48"/>
+    <cellStyle name="60% - Accent 6" xfId="19" builtinId="52"/>
+    <cellStyle name="Accent 1" xfId="20" builtinId="29"/>
+    <cellStyle name="Accent 2" xfId="21" builtinId="33"/>
+    <cellStyle name="Accent 3" xfId="22" builtinId="37"/>
+    <cellStyle name="Accent 4" xfId="23" builtinId="41"/>
+    <cellStyle name="Accent 5" xfId="24" builtinId="45"/>
+    <cellStyle name="Accent 6" xfId="25" builtinId="49"/>
+    <cellStyle name="Bad" xfId="26" builtinId="27"/>
+    <cellStyle name="Calculation" xfId="27" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="28" builtinId="23"/>
+    <cellStyle name="Explanatory Text" xfId="29" builtinId="53"/>
+    <cellStyle name="Good" xfId="30" builtinId="26"/>
+    <cellStyle name="Heading 1" xfId="31" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="32" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="33" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="34" builtinId="19"/>
+    <cellStyle name="Input" xfId="35" builtinId="20"/>
+    <cellStyle name="Linked Cell" xfId="36" builtinId="24"/>
+    <cellStyle name="Neutral" xfId="37" builtinId="28"/>
     <cellStyle name="Note" xfId="38" builtinId="10"/>
     <cellStyle name="Output" xfId="39" builtinId="21"/>
     <cellStyle name="Title" xfId="40" builtinId="15"/>
@@ -1621,7 +1621,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{5E4550A9-F589-46F8-AF7C-B2F7E8155136}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{D89B6D00-8BC5-41FF-A45C-3FA353D7E623}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6306,7 +6306,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{5A67D9B2-0B18-4F4C-8D8A-68F73EB946E1}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{2B341693-8C49-4154-8E05-D8BEE20DE0CD}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6808,7 +6808,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{E88E92C8-7377-49FD-A68C-475D649D2999}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{2879BD91-B97D-4E8F-BC67-D548D89B9EBE}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -11582,7 +11582,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{9A5B782A-8E42-4570-9875-01CF71911754}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{0C92AD6E-B6E1-4319-8EFC-F2B09A059A9E}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
